--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1818,6 +1818,1332 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132627016</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>620553</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6907206</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ca 200 bladrosetter spridda över ca 4 m2</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132627029</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>620619</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6907297</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ca 50 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132627017</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>620567</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6907210</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132627028</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>620564</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6907355</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>30 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132627024</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>620566</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6907351</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>30 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132627020</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>620612</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6907283</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ca 50 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132627021</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>620605</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6907280</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ca 50 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132627015</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>620554</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6907215</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>rikligt med ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132627019</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>620612</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6907246</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ca 50 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132627030</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>620634</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6907281</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ca 80 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132627023</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>620566</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6907307</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132627022</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>620576</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6907314</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132627018</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>620569</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6907223</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>100 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -1823,7 +1823,7 @@
         <v>132627016</v>
       </c>
       <c r="B13" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>132627029</v>
       </c>
       <c r="B14" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>132627017</v>
       </c>
       <c r="B15" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>132627028</v>
       </c>
       <c r="B16" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>132627024</v>
       </c>
       <c r="B17" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>132627020</v>
       </c>
       <c r="B18" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,48 +2427,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132627021</v>
+        <v>132627015</v>
       </c>
       <c r="B19" t="n">
-        <v>99098</v>
+        <v>57949</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620605</v>
+        <v>620554</v>
       </c>
       <c r="R19" t="n">
-        <v>6907280</v>
+        <v>6907215</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2502,7 +2507,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ca 50 bladrosetter</t>
+          <t>rikligt med ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2529,53 +2534,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132627015</v>
+        <v>132627021</v>
       </c>
       <c r="B20" t="n">
-        <v>57948</v>
+        <v>99106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620554</v>
+        <v>620605</v>
       </c>
       <c r="R20" t="n">
-        <v>6907215</v>
+        <v>6907280</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>rikligt med ringhack på tall</t>
+          <t>ca 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2639,7 +2639,7 @@
         <v>132627019</v>
       </c>
       <c r="B21" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>132627030</v>
       </c>
       <c r="B22" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>132627023</v>
       </c>
       <c r="B23" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>132627022</v>
       </c>
       <c r="B24" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>132627018</v>
       </c>
       <c r="B25" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -1823,7 +1823,7 @@
         <v>132627016</v>
       </c>
       <c r="B13" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>132627029</v>
       </c>
       <c r="B14" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>132627017</v>
       </c>
       <c r="B15" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>132627028</v>
       </c>
       <c r="B16" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>132627024</v>
       </c>
       <c r="B17" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>132627020</v>
       </c>
       <c r="B18" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,53 +2427,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132627015</v>
+        <v>132627021</v>
       </c>
       <c r="B19" t="n">
-        <v>57949</v>
+        <v>99116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620554</v>
+        <v>620605</v>
       </c>
       <c r="R19" t="n">
-        <v>6907215</v>
+        <v>6907280</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2507,7 +2502,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>rikligt med ringhack på tall</t>
+          <t>ca 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2534,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132627021</v>
+        <v>132627019</v>
       </c>
       <c r="B20" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,10 +2564,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620605</v>
+        <v>620612</v>
       </c>
       <c r="R20" t="n">
-        <v>6907280</v>
+        <v>6907246</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2636,48 +2631,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132627019</v>
+        <v>132627015</v>
       </c>
       <c r="B21" t="n">
-        <v>99106</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620612</v>
+        <v>620554</v>
       </c>
       <c r="R21" t="n">
-        <v>6907246</v>
+        <v>6907215</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ca 50 bladrosetter</t>
+          <t>rikligt med ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2741,7 +2741,7 @@
         <v>132627030</v>
       </c>
       <c r="B22" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>132627023</v>
       </c>
       <c r="B23" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>132627022</v>
       </c>
       <c r="B24" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>132627018</v>
       </c>
       <c r="B25" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -1823,7 +1823,7 @@
         <v>132627016</v>
       </c>
       <c r="B13" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>132627029</v>
       </c>
       <c r="B14" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>132627017</v>
       </c>
       <c r="B15" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>132627028</v>
       </c>
       <c r="B16" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>132627024</v>
       </c>
       <c r="B17" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>132627020</v>
       </c>
       <c r="B18" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,48 +2427,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132627021</v>
+        <v>132627015</v>
       </c>
       <c r="B19" t="n">
-        <v>99116</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620605</v>
+        <v>620554</v>
       </c>
       <c r="R19" t="n">
-        <v>6907280</v>
+        <v>6907215</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2502,7 +2507,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ca 50 bladrosetter</t>
+          <t>rikligt med ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2529,10 +2534,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132627019</v>
+        <v>132627021</v>
       </c>
       <c r="B20" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2564,10 +2569,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620612</v>
+        <v>620605</v>
       </c>
       <c r="R20" t="n">
-        <v>6907246</v>
+        <v>6907280</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2631,53 +2636,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132627015</v>
+        <v>132627019</v>
       </c>
       <c r="B21" t="n">
-        <v>57953</v>
+        <v>99117</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620554</v>
+        <v>620612</v>
       </c>
       <c r="R21" t="n">
-        <v>6907215</v>
+        <v>6907246</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>rikligt med ringhack på tall</t>
+          <t>ca 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2741,7 +2741,7 @@
         <v>132627030</v>
       </c>
       <c r="B22" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>132627023</v>
       </c>
       <c r="B23" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>132627022</v>
       </c>
       <c r="B24" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>132627018</v>
       </c>
       <c r="B25" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -1823,7 +1823,7 @@
         <v>132627016</v>
       </c>
       <c r="B13" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>132627029</v>
       </c>
       <c r="B14" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>132627028</v>
       </c>
       <c r="B16" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>132627024</v>
       </c>
       <c r="B17" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>132627020</v>
       </c>
       <c r="B18" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>132627021</v>
       </c>
       <c r="B20" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>132627019</v>
       </c>
       <c r="B21" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>132627030</v>
       </c>
       <c r="B22" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,10 +2840,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132627023</v>
+        <v>132627022</v>
       </c>
       <c r="B23" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620566</v>
+        <v>620576</v>
       </c>
       <c r="R23" t="n">
-        <v>6907307</v>
+        <v>6907314</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132627022</v>
+        <v>132627023</v>
       </c>
       <c r="B24" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620576</v>
+        <v>620566</v>
       </c>
       <c r="R24" t="n">
-        <v>6907314</v>
+        <v>6907307</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3047,7 +3047,7 @@
         <v>132627018</v>
       </c>
       <c r="B25" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -2840,7 +2840,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132627022</v>
+        <v>132627023</v>
       </c>
       <c r="B23" t="n">
         <v>99118</v>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620576</v>
+        <v>620566</v>
       </c>
       <c r="R23" t="n">
-        <v>6907314</v>
+        <v>6907307</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132627023</v>
+        <v>132627022</v>
       </c>
       <c r="B24" t="n">
         <v>99118</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620566</v>
+        <v>620576</v>
       </c>
       <c r="R24" t="n">
-        <v>6907307</v>
+        <v>6907314</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -1823,7 +1823,7 @@
         <v>132627016</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>132627029</v>
       </c>
       <c r="B14" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>132627017</v>
       </c>
       <c r="B15" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>132627028</v>
       </c>
       <c r="B16" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>132627024</v>
       </c>
       <c r="B17" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>132627020</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>132627015</v>
       </c>
       <c r="B19" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>132627021</v>
       </c>
       <c r="B20" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>132627019</v>
       </c>
       <c r="B21" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>132627030</v>
       </c>
       <c r="B22" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,10 +2840,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132627023</v>
+        <v>132627022</v>
       </c>
       <c r="B23" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620566</v>
+        <v>620576</v>
       </c>
       <c r="R23" t="n">
-        <v>6907307</v>
+        <v>6907314</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132627022</v>
+        <v>132627023</v>
       </c>
       <c r="B24" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620576</v>
+        <v>620566</v>
       </c>
       <c r="R24" t="n">
-        <v>6907314</v>
+        <v>6907307</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3047,7 +3047,7 @@
         <v>132627018</v>
       </c>
       <c r="B25" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -2840,7 +2840,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132627022</v>
+        <v>132627023</v>
       </c>
       <c r="B23" t="n">
         <v>99130</v>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620576</v>
+        <v>620566</v>
       </c>
       <c r="R23" t="n">
-        <v>6907314</v>
+        <v>6907307</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132627023</v>
+        <v>132627022</v>
       </c>
       <c r="B24" t="n">
         <v>99130</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620566</v>
+        <v>620576</v>
       </c>
       <c r="R24" t="n">
-        <v>6907307</v>
+        <v>6907314</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -2427,53 +2427,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132627015</v>
+        <v>132627021</v>
       </c>
       <c r="B19" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620554</v>
+        <v>620605</v>
       </c>
       <c r="R19" t="n">
-        <v>6907215</v>
+        <v>6907280</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2507,7 +2502,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>rikligt med ringhack på tall</t>
+          <t>ca 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2534,7 +2529,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132627021</v>
+        <v>132627019</v>
       </c>
       <c r="B20" t="n">
         <v>99130</v>
@@ -2569,10 +2564,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620605</v>
+        <v>620612</v>
       </c>
       <c r="R20" t="n">
-        <v>6907280</v>
+        <v>6907246</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2636,48 +2631,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132627019</v>
+        <v>132627015</v>
       </c>
       <c r="B21" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620612</v>
+        <v>620554</v>
       </c>
       <c r="R21" t="n">
-        <v>6907246</v>
+        <v>6907215</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ca 50 bladrosetter</t>
+          <t>rikligt med ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2840,7 +2840,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132627023</v>
+        <v>132627018</v>
       </c>
       <c r="B23" t="n">
         <v>99130</v>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620566</v>
+        <v>620569</v>
       </c>
       <c r="R23" t="n">
-        <v>6907307</v>
+        <v>6907223</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>20 bladrosetter</t>
+          <t>100 bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2942,7 +2942,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132627022</v>
+        <v>132627023</v>
       </c>
       <c r="B24" t="n">
         <v>99130</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620576</v>
+        <v>620566</v>
       </c>
       <c r="R24" t="n">
-        <v>6907314</v>
+        <v>6907307</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3044,7 +3044,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132627018</v>
+        <v>132627022</v>
       </c>
       <c r="B25" t="n">
         <v>99130</v>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620569</v>
+        <v>620576</v>
       </c>
       <c r="R25" t="n">
-        <v>6907223</v>
+        <v>6907314</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>100 bladrosetter</t>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -2427,48 +2427,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132627021</v>
+        <v>132627015</v>
       </c>
       <c r="B19" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620605</v>
+        <v>620554</v>
       </c>
       <c r="R19" t="n">
-        <v>6907280</v>
+        <v>6907215</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2502,7 +2507,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ca 50 bladrosetter</t>
+          <t>rikligt med ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2529,7 +2534,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132627019</v>
+        <v>132627021</v>
       </c>
       <c r="B20" t="n">
         <v>99130</v>
@@ -2564,10 +2569,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620612</v>
+        <v>620605</v>
       </c>
       <c r="R20" t="n">
-        <v>6907246</v>
+        <v>6907280</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2631,53 +2636,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132627015</v>
+        <v>132627019</v>
       </c>
       <c r="B21" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620554</v>
+        <v>620612</v>
       </c>
       <c r="R21" t="n">
-        <v>6907215</v>
+        <v>6907246</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>rikligt med ringhack på tall</t>
+          <t>ca 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2840,7 +2840,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132627018</v>
+        <v>132627023</v>
       </c>
       <c r="B23" t="n">
         <v>99130</v>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620569</v>
+        <v>620566</v>
       </c>
       <c r="R23" t="n">
-        <v>6907223</v>
+        <v>6907307</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>100 bladrosetter</t>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2942,7 +2942,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132627023</v>
+        <v>132627022</v>
       </c>
       <c r="B24" t="n">
         <v>99130</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620566</v>
+        <v>620576</v>
       </c>
       <c r="R24" t="n">
-        <v>6907307</v>
+        <v>6907314</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3044,7 +3044,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132627022</v>
+        <v>132627018</v>
       </c>
       <c r="B25" t="n">
         <v>99130</v>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620576</v>
+        <v>620569</v>
       </c>
       <c r="R25" t="n">
-        <v>6907314</v>
+        <v>6907223</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>20 bladrosetter</t>
+          <t>100 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3144,6 +3144,103 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133816706</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79872</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1353</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Trådbrosklav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ramalina thrausta</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kulåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>620552</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6907124</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -3149,7 +3149,7 @@
         <v>133816706</v>
       </c>
       <c r="B26" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -3149,7 +3149,7 @@
         <v>133816706</v>
       </c>
       <c r="B26" t="n">
-        <v>79873</v>
+        <v>79887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -3149,7 +3149,7 @@
         <v>133816706</v>
       </c>
       <c r="B26" t="n">
-        <v>79887</v>
+        <v>79897</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -3149,7 +3149,7 @@
         <v>133816706</v>
       </c>
       <c r="B26" t="n">
-        <v>79897</v>
+        <v>79898</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -3149,7 +3149,7 @@
         <v>133816706</v>
       </c>
       <c r="B26" t="n">
-        <v>79898</v>
+        <v>79905</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102531588</v>
+        <v>129578078</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åh, Mpd</t>
+          <t>Åh, Åh, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620593.2201437417</v>
+        <v>620456</v>
       </c>
       <c r="R2" t="n">
-        <v>6907289.4990068</v>
+        <v>6907245</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spridd på ett flertal senvuxna granar i området</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112038656</v>
+        <v>113018043</v>
       </c>
       <c r="B3" t="n">
-        <v>89115</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5754</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620484</v>
+        <v>620645</v>
       </c>
       <c r="R3" t="n">
-        <v>6907328</v>
+        <v>6907289</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,12 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113018043</v>
+        <v>129577446</v>
       </c>
       <c r="B4" t="n">
-        <v>90045</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,14 +905,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Åh, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620644</v>
+        <v>620486</v>
       </c>
       <c r="R4" t="n">
-        <v>6907290</v>
+        <v>6907249</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -964,12 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113018042</v>
+        <v>132627017</v>
       </c>
       <c r="B5" t="n">
-        <v>90430</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,32 +982,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620606</v>
+        <v>620567</v>
       </c>
       <c r="R5" t="n">
-        <v>6907271</v>
+        <v>6907210</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1064,17 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,64 +1050,63 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127291532</v>
+        <v>133816706</v>
       </c>
       <c r="B6" t="n">
-        <v>92633</v>
+        <v>79912</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>1353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åh, Åh, Mpd</t>
+          <t>Kulåsen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620569</v>
+        <v>620552</v>
       </c>
       <c r="R6" t="n">
-        <v>6907190</v>
+        <v>6907124</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1167,22 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,37 +1165,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127292086</v>
+        <v>132627032</v>
       </c>
       <c r="B7" t="n">
-        <v>91758</v>
+        <v>96413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6040186</v>
+        <v>2809</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Å, Å, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620510</v>
+        <v>620624</v>
       </c>
       <c r="R7" t="n">
         <v>6907248</v>
@@ -1269,22 +1230,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,22 +1250,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127291446</v>
+        <v>127291532</v>
       </c>
       <c r="B8" t="n">
-        <v>90896</v>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5754</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620539</v>
+        <v>620569</v>
       </c>
       <c r="R8" t="n">
-        <v>6907155</v>
+        <v>6907190</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1381,7 +1332,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1391,7 +1342,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1418,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129577446</v>
+        <v>112038656</v>
       </c>
       <c r="B9" t="n">
-        <v>91605</v>
+        <v>91443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,34 +1380,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5754</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åh, Åh, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620486</v>
+        <v>620484</v>
       </c>
       <c r="R9" t="n">
-        <v>6907249</v>
+        <v>6907328</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1483,12 +1434,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129577482</v>
+        <v>127291446</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>91443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,43 +1477,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5754</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Åh, Åh, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620471</v>
+        <v>620539</v>
       </c>
       <c r="R10" t="n">
-        <v>6907238</v>
+        <v>6907155</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1589,12 +1531,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1621,45 +1573,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129578097</v>
+        <v>129577482</v>
       </c>
       <c r="B11" t="n">
-        <v>80096</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Åh, Åh, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620464</v>
+        <v>620471</v>
       </c>
       <c r="R11" t="n">
-        <v>6907252</v>
+        <v>6907238</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1718,32 +1679,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129578078</v>
+        <v>129578097</v>
       </c>
       <c r="B12" t="n">
-        <v>79119</v>
+        <v>80336</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620456</v>
+        <v>620464</v>
       </c>
       <c r="R12" t="n">
-        <v>6907245</v>
+        <v>6907252</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1789,11 +1750,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Spridd på ett flertal senvuxna granar i området</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,48 +1776,62 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132627016</v>
+        <v>127291750</v>
       </c>
       <c r="B13" t="n">
-        <v>99130</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Åh, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620553</v>
+        <v>620622</v>
       </c>
       <c r="R13" t="n">
-        <v>6907206</v>
+        <v>6907237</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,17 +1855,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ca 200 bladrosetter spridda över ca 4 m2</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1910,60 +1885,65 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132627029</v>
+        <v>132627014</v>
       </c>
       <c r="B14" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620619</v>
+        <v>620542</v>
       </c>
       <c r="R14" t="n">
-        <v>6907297</v>
+        <v>6907069</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1993,11 +1973,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ca 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2024,10 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132627017</v>
+        <v>132627015</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2035,37 +2010,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620567</v>
+        <v>620554</v>
       </c>
       <c r="R15" t="n">
-        <v>6907210</v>
+        <v>6907215</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2095,6 +2075,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>rikligt med ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2121,10 +2106,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132627028</v>
+        <v>102531543</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2150,19 +2135,23 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620564</v>
+        <v>620444</v>
       </c>
       <c r="R16" t="n">
-        <v>6907355</v>
+        <v>6907301</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2186,17 +2175,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>30 bladrosetter</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,28 +2189,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132627024</v>
+        <v>102531588</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,19 +2237,23 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620566</v>
+        <v>620593</v>
       </c>
       <c r="R17" t="n">
-        <v>6907351</v>
+        <v>6907289</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2288,17 +2277,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>30 bladrosetter</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2307,28 +2291,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132627020</v>
+        <v>102531602</v>
       </c>
       <c r="B18" t="n">
-        <v>99130</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2354,19 +2339,23 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620612</v>
+        <v>620635</v>
       </c>
       <c r="R18" t="n">
-        <v>6907283</v>
+        <v>6907258</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2390,17 +2379,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>ca 50 bladrosetter</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,71 +2393,67 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132627015</v>
+        <v>132627016</v>
       </c>
       <c r="B19" t="n">
-        <v>57958</v>
+        <v>99195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620554</v>
+        <v>620553</v>
       </c>
       <c r="R19" t="n">
-        <v>6907215</v>
+        <v>6907206</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2507,7 +2487,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>rikligt med ringhack på tall</t>
+          <t>ca 200 bladrosetter spridda över ca 4 m2</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2534,10 +2514,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132627021</v>
+        <v>132627018</v>
       </c>
       <c r="B20" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,10 +2549,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620605</v>
+        <v>620569</v>
       </c>
       <c r="R20" t="n">
-        <v>6907280</v>
+        <v>6907223</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2609,7 +2589,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ca 50 bladrosetter</t>
+          <t>100 bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2639,7 +2619,7 @@
         <v>132627019</v>
       </c>
       <c r="B21" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,10 +2718,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132627030</v>
+        <v>132627020</v>
       </c>
       <c r="B22" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2773,10 +2753,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620634</v>
+        <v>620612</v>
       </c>
       <c r="R22" t="n">
-        <v>6907281</v>
+        <v>6907283</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2813,7 +2793,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ca 80 bladrosetter</t>
+          <t>ca 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2840,10 +2820,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132627023</v>
+        <v>132627021</v>
       </c>
       <c r="B23" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2875,10 +2855,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620566</v>
+        <v>620605</v>
       </c>
       <c r="R23" t="n">
-        <v>6907307</v>
+        <v>6907280</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2915,7 +2895,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>20 bladrosetter</t>
+          <t>ca 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2945,7 +2925,7 @@
         <v>132627022</v>
       </c>
       <c r="B24" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3044,10 +3024,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132627018</v>
+        <v>132627023</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3079,10 +3059,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620569</v>
+        <v>620566</v>
       </c>
       <c r="R25" t="n">
-        <v>6907223</v>
+        <v>6907307</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3119,7 +3099,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>100 bladrosetter</t>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3146,45 +3126,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133816706</v>
+        <v>132627024</v>
       </c>
       <c r="B26" t="n">
-        <v>79905</v>
+        <v>99195</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1353</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kulåsen, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620552</v>
+        <v>620566</v>
       </c>
       <c r="R26" t="n">
-        <v>6907124</v>
+        <v>6907351</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3211,12 +3191,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>30 bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3231,15 +3216,636 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132627028</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>620564</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6907355</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>30 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132627029</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>620619</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6907297</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ca 50 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132627030</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>620634</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6907281</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ca 80 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132627031</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>620645</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6907255</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ca 50 bladroestter</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>113018042</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>620606</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6907271</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127292086</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Å, Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>620510</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6907248</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129578078</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113018043</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129577446</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627017</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133816706</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627032</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1366,6 +1401,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127291532</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038656</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127291446</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1676,6 +1726,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129577482</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1773,6 +1828,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129578097</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1894,6 +1954,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127291750</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1996,6 +2061,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627014</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2103,6 +2173,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627015</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2205,6 +2280,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102531543</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2307,6 +2387,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102531588</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2409,6 +2494,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102531602</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2511,6 +2601,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627016</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2613,6 +2708,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627018</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2715,6 +2815,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627019</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2817,6 +2922,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627020</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2919,6 +3029,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627021</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3021,6 +3136,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627022</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3123,6 +3243,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627023</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3225,6 +3350,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627024</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3327,6 +3457,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627028</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3429,6 +3564,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627029</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3531,6 +3671,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627030</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3633,6 +3778,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627031</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3739,6 +3889,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113018042</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3846,8 +4001,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127292086</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>